--- a/Vadodara-March-2026.xlsx
+++ b/Vadodara-March-2026.xlsx
@@ -112,7 +112,7 @@
     <t>AMAZE</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>15/05/2025</t>
